--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\eclipse-workspace\BlazeDemo\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD4F6CE-FEF6-4B90-9744-49BEEA260D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F53F4C-1E4B-47AC-AD1A-529B2B757F7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{8401687E-FC8E-4735-9E79-1C2BDA1EE956}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>departure</t>
   </si>
@@ -60,25 +60,82 @@
     <t>Paris</t>
   </si>
   <si>
-    <t>Buenos Aires</t>
-  </si>
-  <si>
     <t>John Doe</t>
   </si>
   <si>
-    <t>123 Main St</t>
-  </si>
-  <si>
-    <t>Anytown</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
     <t>Visa</t>
   </si>
   <si>
-    <t>4242 4242 4242 4242</t>
+    <t>London</t>
+  </si>
+  <si>
+    <t>John##Doe!!</t>
+  </si>
+  <si>
+    <t>123 Tech Lane</t>
+  </si>
+  <si>
+    <t>Noida</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>FOUR_ONE_ONE_ONE</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>Amit_Sharma_$$</t>
+  </si>
+  <si>
+    <t>456 IT Hub</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Mastercard</t>
+  </si>
+  <si>
+    <t>XYZ-INVALID-CARD</t>
+  </si>
+  <si>
+    <t>Amit Sharma</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>Berlin</t>
+  </si>
+  <si>
+    <t>&lt;Admin&gt;</t>
+  </si>
+  <si>
+    <t>789 Web Drive</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t>American Express</t>
+  </si>
+  <si>
+    <t>0000AAAA0000</t>
+  </si>
+  <si>
+    <t>Admin</t>
   </si>
 </sst>
 </file>
@@ -457,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F0ADA3E-B84F-4869-A43C-CB46785BD0D8}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.81640625" customWidth="1"/>
@@ -467,11 +524,11 @@
     <col min="5" max="5" width="15.7265625" customWidth="1"/>
     <col min="6" max="6" width="13.36328125" customWidth="1"/>
     <col min="8" max="8" width="12.90625" customWidth="1"/>
-    <col min="9" max="9" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.26953125" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" customWidth="1"/>
+    <col min="10" max="10" width="19.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -508,31 +565,95 @@
         <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1">
+        <v>201301</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="1">
-        <v>12345</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>12</v>
+    </row>
+    <row r="3" spans="1:10" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="1">
+        <v>560001</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1">
+        <v>400001</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
